--- a/macro/양식/캠페인_취소삭제_양식.xlsx
+++ b/macro/양식/캠페인_취소삭제_양식.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -462,11 +462,6 @@
           <t>비즈핏취소</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>유입플환불</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,11 +485,6 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
